--- a/pensum/ok05/OK05_Kalkulasjon_Oppgaver_v6.xlsx
+++ b/pensum/ok05/OK05_Kalkulasjon_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="277">
   <si>
     <t xml:space="preserve">Kalkulasjon og kalkyleprinsipper: oppgaver til kapittel 5</t>
   </si>
@@ -238,7 +238,16 @@
     <t xml:space="preserve">j) Tom vil ha 950 kr, Ronny vil beholde 890. Skriv to setninger til dem med tallene fra oppstillingen: hva går lønna til, og hva er det som flytter prisen mest?</t>
   </si>
   <si>
+    <t xml:space="preserve">Han har glemt de indirekte kostnadene, og regnet fortjenesten av feil tall</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Fastpris til Hansen: hele selvkostkalkylen på jobb 2614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Han har brukt feil sats for merverdiavgift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenting, 27 384 er riktig</t>
   </si>
   <si>
     <t xml:space="preserve">Hansen vil ha fastpris på å bytte sikringsskapet i eneboligen (jobb 2614 fra kapittel 2). Ida har anslått 14 montørtimer, materiell for 9 800 kr og kjøring for 800 kr. Hun setter opp kalkylen slik boka gjør det i eksempel 3, helt fram til prisen med merverdiavgift. Tom har regnet på egen hånd og fått 27 384 kr.</t>
@@ -327,7 +336,16 @@
     <t xml:space="preserve">f) Prisen er fastpris, så timene er Nordlys' risiko. Hva gjør Nordlys før og under jobben for å holde seg på 14 timer? To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Si nei til 22 000: jobben fortrenger jobber til normalpris</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2A: 20 skap til 22 000 kr i en stille januar: ta jobben?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si ja: dekningsbidraget er positivt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Si ja, men bare for ti skap</t>
   </si>
   <si>
     <t xml:space="preserve">Januar 2027. Ordreboka er tynn, og fire montører har lite å gjøre de neste tre ukene. Et boligbyggelag vil ha byttet 20 sikringsskap av samme type som hos Hansen, og tilbyr 22 000 kr per skap uten merverdiavgift. Tom sier nei: under selvkost. Kari sier ja: husleia, kontoret og bilene koster det samme uansett.</t>
@@ -369,7 +387,16 @@
     <t xml:space="preserve">g) Etter januar vil Tom bruke 22 000 kr som fast pris på alle skapbytter resten av året, siden «dekningsbidraget er positivt». Hva sier du til ham? To setninger med tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kostnaden ble høyere enn kalkulert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2B: Etterkalkylen på jobb 2614: holdt forkalkylen?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nordlys tjente 3 200 kr mer enn kalkulert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeprisen var for lav</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys har byttet tre sikringsskap av Hansen-typen til fastpris 26 611,20 kr uten merverdiavgift, kalkulert med 14 timer. Timelistene sier 19 timer på alle tre. Materiell og kjøring holdt. Ida setter opp etterkalkylen slik boka gjør i tabell 5.1, og spør hva Nordlys gjør med neste tilbud.</t>
@@ -464,7 +491,16 @@
     <t xml:space="preserve">e) Tre jobber på rad tok 19 timer. Hva gjør Nordlys med neste tilbud? Skriv to setninger med tall: én om forkalkylen og én om hvordan jobben gjennomføres.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lager, svinn, bestilling, bundet kapital og en del av de indirekte kostnadene</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2C: Downlights fra Polarlys: pris, avanse og bruttofortjeneste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare fortjeneste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merverdiavgiften</t>
   </si>
   <si>
     <t xml:space="preserve">Ida har bestilt et parti downlights fra Polarlys til et borettslag. Nordlys fakturerer materiellet videre med 20 % påslag på inntakskosten. Kunden har sett prisen i en nettbutikk og spør hvorfor Nordlys tar mer. Og Tom lurer på hvorfor 40 % pluss 12 % i bokas eksempel ikke blir 52 %.</t>
@@ -770,9 +806,6 @@
     <t xml:space="preserve">2B c) Minustegnet</t>
   </si>
   <si>
-    <t xml:space="preserve">Kostnaden ble høyere enn kalkulert</t>
-  </si>
-  <si>
     <t xml:space="preserve">2B d) Ny pris med 19 timer</t>
   </si>
   <si>
@@ -834,9 +867,6 @@
   </si>
   <si>
     <t xml:space="preserve">2C i) Påslaget dekker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lager, svinn, bestilling, bundet kapital og en del av de indirekte kostnadene</t>
   </si>
   <si>
     <t xml:space="preserve">2C j) Til kunden</t>
@@ -1030,7 +1060,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1129,6 +1159,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2389,7 +2423,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G47"/>
+  <dimension ref="B1:Z47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2397,17 +2431,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="25" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2418,6 +2461,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="25" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2431,7 +2477,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2451,7 +2497,7 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2471,7 +2517,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2481,7 +2527,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>25</v>
@@ -2489,65 +2535,65 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>9800</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="25" t="n">
+        <v>78</v>
+      </c>
+      <c r="C14" s="26" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C16" s="17"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" s="17"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C18" s="17"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C19" s="17"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" s="17"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C21" s="17"/>
     </row>
@@ -2563,7 +2609,7 @@
     </row>
     <row r="24" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -2573,12 +2619,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C27" s="24" t="str">
         <f aca="false">IF(C12="","Skriv svaret i cellen C12.",IF(C12=(14*640),"Riktig.",IF(ABS(C12-(14*890))&lt;=0,"Du har brukt timeprisen 890. I kalkylen brukes direkte lønnskostnad, 640 kr per time; fortjenesten kommer senere.","Ikke riktig ennå. 14 timer ganger 640 kr.")))</f>
@@ -2591,7 +2637,7 @@
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C28" s="24" t="str">
         <f aca="false">IF(C15="","Skriv svaret i cellen C15.",IF(C15=(14*640+9800+800),"Riktig.",IF(ABS(C15-(14*640+9800))&lt;=0,"Du har glemt kjøringen, 800 kr. Den er en direkte kostnad.","Ikke riktig ennå. Direkte lønn pluss materiell pluss kjøring.")))</f>
@@ -2604,7 +2650,7 @@
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C29" s="24" t="str">
         <f aca="false">IF(C16="","Skriv svaret i cellen C16.",IF(C16=(14*300),"Riktig.",IF(ABS(C16-(300))&lt;=0,"Tilleggssatsen er 300 kr per montørtime, og jobben har 14 timer.","Ikke riktig ennå. 14 timer ganger 300 kr.")))</f>
@@ -2617,7 +2663,7 @@
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C30" s="24" t="str">
         <f aca="false">IF(C17="","Skriv svaret i cellen C17.",IF(C17=(14*640+9800+800+14*300),"Riktig.",IF(ABS(C17-(14*640+9800+800))&lt;=0,"Det er bare de direkte kostnadene. Legg til de indirekte, 4 200.","Ikke riktig ennå. Sum direkte pluss indirekte.")))</f>
@@ -2630,7 +2676,7 @@
     </row>
     <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C31" s="24" t="str">
         <f aca="false">IF(C18="","Skriv svaret i cellen C18.",IF(ABS(C18-((14*640+9800+800+14*300)*0.12))&lt;=0.01,"Riktig.",IF(ABS(C18-((14*640+9800+800)*0.12))&lt;=0.01,"Du har regnet 12 % av de direkte kostnadene. Fortjenesten regnes av selvkost, 23 760.","Ikke riktig ennå. 12 % av selvkost.")))</f>
@@ -2643,7 +2689,7 @@
     </row>
     <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C32" s="24" t="str">
         <f aca="false">IF(C19="","Skriv svaret i cellen C19.",IF(ABS(C19-((14*640+9800+800+14*300)*1.12))&lt;=0.01,"Riktig.",IF(ABS(C19-((14*640+9800+800)*1.12))&lt;=0.01,"Du har lagt fortjenesten på de direkte kostnadene. Den legges på selvkost, 23 760.","Ikke riktig ennå. Selvkost pluss fortjeneste.")))</f>
@@ -2656,7 +2702,7 @@
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C33" s="24" t="str">
         <f aca="false">IF(C20="","Skriv svaret i cellen C20.",IF(ABS(C20-((14*640+9800+800+14*300)*1.12*0.25))&lt;=0.01,"Riktig.",IF(ABS(C20-((14*640+9800+800+14*300)*0.25))&lt;=0.01,"Du har regnet merverdiavgift av selvkost. Den regnes av prisen uten merverdiavgift, 26 611,20.","Ikke riktig ennå. 25 % av prisen uten merverdiavgift.")))</f>
@@ -2669,7 +2715,7 @@
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C34" s="24" t="str">
         <f aca="false">IF(C21="","Skriv svaret i cellen C21.",IF(ABS(C21-((14*640+9800+800+14*300)*1.12*1.25))&lt;=0.01,"Riktig.",IF(ABS(C21-((14*640+9800+800)*1.12*1.25))&lt;=0.01,"Det er Toms regnestykke: de indirekte kostnadene mangler, og fortjenesten er regnet av feil tall.","Ikke riktig ennå. Pris uten merverdiavgift pluss merverdiavgift.")))</f>
@@ -2682,7 +2728,7 @@
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C36" s="21"/>
       <c r="G36" s="16" t="str">
@@ -2692,11 +2738,11 @@
     </row>
     <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="26"/>
+        <v>97</v>
+      </c>
+      <c r="C37" s="27"/>
       <c r="D37" s="15" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G37" s="16" t="str">
         <f aca="false">IF(C37="","Skriv svaret i den gule cellen.",IF(ABS(C37-(ROUND((14*640+9800+800+14*300)*0.12/640,1)))&lt;=0.05,"Riktig.",IF(ABS(C37-(ROUND((14*640+9800+800+14*300)*0.12/890,1)))&lt;=0.05,"Du har delt på timeprisen 890. Hver ekstra time koster Nordlys 640 kr i direkte lønn; del på 640.",IF(ABS(C37-(ROUND((14*640+9800+800+14*300)*0.12/(640+300),1)))&lt;=0.05,"Du har tatt med 300 kr i indirekte per time. Nordlys legger de indirekte på som fast beløp per skap, så en ekstra time koster bare 640.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -2705,7 +2751,7 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -2883,7 +2929,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Han har glemt de indirekte kostnadene,og regnet fortjenesten av feil tall,Han har brukt feil sats for merverdiavgift,Ingenting,27 384 er riktig"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C44" type="list">
@@ -2906,7 +2952,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G31"/>
+  <dimension ref="B1:Z31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2914,17 +2960,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="25" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2935,6 +2990,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="25" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2948,7 +3006,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2968,7 +3026,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2988,7 +3046,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3008,7 +3066,7 @@
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -3018,7 +3076,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="15" t="s">
@@ -3031,7 +3089,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="15" t="s">
@@ -3044,11 +3102,11 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="26"/>
+        <v>110</v>
+      </c>
+      <c r="C17" s="27"/>
       <c r="D17" s="15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G17" s="16" t="str">
         <f aca="false">IF(C17="","Skriv svaret i den gule cellen.",IF(ABS(C17-(ROUND((22000-19560)/22000*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C17-(ROUND((22000-19560)/19560*100,1)))&lt;=0.05,"Du har delt på merkost. Dekningsgraden regnes av prisen, 22 000.",IF(ABS(C17-(ROUND((22000-19560)/26611.2*100,1)))&lt;=0.05,"Du har delt på normalprisen. Her er prisen 22 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
@@ -3057,7 +3115,7 @@
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="15" t="s">
@@ -3070,11 +3128,11 @@
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="26"/>
+        <v>113</v>
+      </c>
+      <c r="C19" s="27"/>
       <c r="D19" s="15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G19" s="16" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(ABS(C19-(ROUND(20*(22000-19560)/(20*4200)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C19-(ROUND(20*(22000-19560)/(20*23760)*100,1)))&lt;=0.05,"Du har delt på selvkosten. Del på de indirekte kostnadene, 84 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
@@ -3083,7 +3141,7 @@
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C21" s="21"/>
       <c r="G21" s="16" t="str">
@@ -3093,7 +3151,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -3231,7 +3289,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Si nei til 22 000: jobben fortrenger jobber til normalpris,Si ja: dekningsbidraget er positivt,Si ja,men bare for ti skap"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
@@ -3254,7 +3312,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G48"/>
+  <dimension ref="B1:Z48"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3262,17 +3320,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="25" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -3283,6 +3350,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="25" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -3296,7 +3366,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3316,7 +3386,7 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3336,7 +3406,7 @@
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3346,128 +3416,128 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="25" t="n">
+        <v>128</v>
+      </c>
+      <c r="C12" s="26" t="n">
         <v>8960</v>
       </c>
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
-      <c r="F12" s="26"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="25" t="n">
+        <v>129</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <v>9800</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <v>9800</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="25" t="n">
+        <v>130</v>
+      </c>
+      <c r="C14" s="26" t="n">
         <v>800</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <v>800</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="25" t="n">
+        <v>79</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <v>19560</v>
       </c>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
-      <c r="F15" s="26"/>
+      <c r="F15" s="27"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="25" t="n">
+        <v>131</v>
+      </c>
+      <c r="C16" s="26" t="n">
         <v>4200</v>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="26" t="n">
         <v>4200</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="25" t="n">
+        <v>81</v>
+      </c>
+      <c r="C17" s="26" t="n">
         <v>23760</v>
       </c>
       <c r="D17" s="17"/>
       <c r="E17" s="17"/>
-      <c r="F17" s="26"/>
+      <c r="F17" s="27"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="25" t="n">
+        <v>132</v>
+      </c>
+      <c r="C18" s="26" t="n">
         <v>26611.2</v>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="26" t="n">
         <v>26611.2</v>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="25" t="n">
+        <v>133</v>
+      </c>
+      <c r="C19" s="26" t="n">
         <v>2851.2</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
-      <c r="F19" s="25"/>
+      <c r="F19" s="26"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
@@ -3481,7 +3551,7 @@
     </row>
     <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="8" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -3491,12 +3561,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="23" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C25" s="24" t="str">
         <f aca="false">IF(D12="","Skriv svaret i cellen D12.",IF(D12=(19*640),"Riktig.",IF(ABS(D12-(5*640))&lt;=0,"Det er bare de fem ekstra timene. Etterkalkylen viser hele kostnaden: 19 × 640.",IF(ABS(D12-(19*890))&lt;=0,"Du har brukt timeprisen. I kalkylen er direkte lønn 640 kr per time.","Ikke riktig ennå. 19 timer ganger 640 kr."))))</f>
@@ -3509,7 +3579,7 @@
     </row>
     <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C26" s="24" t="str">
         <f aca="false">IF(E12="","Skriv svaret i cellen E12.",IF(E12=(8960-19*640),"Riktig.",IF(ABS(E12-(19*640-8960))&lt;=0,"Riktig tall, feil fortegn. Forkalkyle minus etterkalkyle; kostnaden ble høyere, så avviket er negativt.","Ikke riktig ennå. Forkalkyle 8 960 minus etterkalkyle 12 160.")))</f>
@@ -3522,7 +3592,7 @@
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C27" s="24" t="str">
         <f aca="false">IF(F12="","Skriv svaret i cellen F12.",IF(ABS(F12-(ROUND((8960-19*640)/8960*100,1)))&lt;=0.05,"Riktig.",IF(ABS(F12-(ROUND((8960-19*640)/(19*640)*100,1)))&lt;=0.05,"Du har delt på etterkalkylen. Avvik i prosent regnes av forkalkylen, 8 960.",IF(ABS(F12-(ROUND((19*640-8960)/8960*100,1)))&lt;=0.05,"Riktig tall, feil fortegn. Kostnaden ble høyere, så avviket er negativt.","Ikke riktig ennå. Avviket i kroner delt på forkalkylen 8 960, ganger 100."))))</f>
@@ -3535,7 +3605,7 @@
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C28" s="24" t="str">
         <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(D15=(19*640+9800+800),"Riktig.",IF(ABS(D15-(19*640+9800))&lt;=0,"Du har glemt kjøringen, 800.","Ikke riktig ennå. 12 160 + 9 800 + 800.")))</f>
@@ -3548,7 +3618,7 @@
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="0" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C29" s="24" t="str">
         <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(E15=(19560-(19*640+9800+800)),"Riktig.",IF(ABS(E15-((19*640+9800+800)-19560))&lt;=0,"Riktig tall, feil fortegn: forkalkyle minus etterkalkyle.","Ikke riktig ennå. 19 560 minus 22 760.")))</f>
@@ -3561,7 +3631,7 @@
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="0" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C30" s="24" t="str">
         <f aca="false">IF(F15="","Skriv svaret i cellen F15.",IF(ABS(F15-(ROUND((19560-(19*640+9800+800))/19560*100,1)))&lt;=0.05,"Riktig.",IF(ABS(F15-(ROUND((19560-(19*640+9800+800))/8960*100,1)))&lt;=0.05,"Du har delt på direkte lønn. Del på forkalkylens sum direkte, 19 560.","Ikke riktig ennå. −3 200 delt på 19 560, ganger 100.")))</f>
@@ -3574,7 +3644,7 @@
     </row>
     <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="0" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C31" s="24" t="str">
         <f aca="false">IF(D17="","Skriv svaret i cellen D17.",IF(D17=(19*640+9800+800+4200),"Riktig.",IF(ABS(D17-(19*640+9800+800+19*300))&lt;=0,"Du har økt de indirekte med timene. Nordlys legger dem på som fast beløp per skap, 4 200, så de står stille.","Ikke riktig ennå. Sum direkte 22 760 pluss indirekte 4 200.")))</f>
@@ -3587,7 +3657,7 @@
     </row>
     <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="0" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C32" s="24" t="str">
         <f aca="false">IF(E17="","Skriv svaret i cellen E17.",IF(E17=(23760-(19*640+9800+800+4200)),"Riktig.",IF(ABS(E17-((19*640+9800+800+4200)-23760))&lt;=0,"Riktig tall, feil fortegn: forkalkyle minus etterkalkyle.","Ikke riktig ennå. 23 760 minus 26 960.")))</f>
@@ -3600,7 +3670,7 @@
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="0" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C33" s="24" t="str">
         <f aca="false">IF(F17="","Skriv svaret i cellen F17.",IF(ABS(F17-(ROUND((23760-(19*640+9800+800+4200))/23760*100,1)))&lt;=0.05,"Riktig.","Ikke riktig ennå. −3 200 delt på 23 760, ganger 100."))</f>
@@ -3613,7 +3683,7 @@
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C34" s="24" t="str">
         <f aca="false">IF(D19="","Skriv svaret i cellen D19.",IF(ABS(D19-(26611.2-(19*640+9800+800+4200)))&lt;=0.01,"Riktig.",IF(ABS(D19-((19*640+9800+800+4200)-26611.2))&lt;=0.01,"Feil fortegn. Fortjeneste er pris minus selvkost; prisen er lavere enn selvkosten, så fortjenesten er negativ.",IF(ABS(D19-(2851.2))&lt;=0.01,"Det er forkalkylens fortjeneste. Prisen er den samme, men selvkosten steg til 26 960.","Ikke riktig ennå. Fastpris 26 611,20 minus selvkost 26 960."))))</f>
@@ -3626,7 +3696,7 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C35" s="24" t="str">
         <f aca="false">IF(E19="","Skriv svaret i cellen E19.",IF(ABS(E19-((26611.2-(19*640+9800+800+4200))-2851.2))&lt;=0.01,"Riktig.",IF(ABS(E19-(2851.2-(26611.2-(19*640+9800+800+4200))))&lt;=0.01,"Riktig tall, feil fortegn. For fortjenesten er avviket etterkalkyle minus forkalkyle, slik at minus alltid betyr dårligere.","Ikke riktig ennå. Etterkalkylens fortjeneste −348,80 minus forkalkylens 2 851,20.")))</f>
@@ -3639,7 +3709,7 @@
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C37" s="21"/>
       <c r="G37" s="16" t="str">
@@ -3649,7 +3719,7 @@
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="15" t="s">
@@ -3662,7 +3732,7 @@
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="8" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -3867,7 +3937,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Kostnaden ble høyere enn kalkulert,Nordlys tjente 3 200 kr mer enn kalkulert,Timeprisen var for lav"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45" type="list">
@@ -3890,7 +3960,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G35"/>
+  <dimension ref="B1:Z35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3898,17 +3968,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="25" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -3919,6 +3998,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="25" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -3932,7 +4014,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3952,7 +4034,7 @@
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3972,7 +4054,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3992,7 +4074,7 @@
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -4002,7 +4084,7 @@
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="15" t="s">
@@ -4015,7 +4097,7 @@
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="15" t="s">
@@ -4028,7 +4110,7 @@
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="15" t="s">
@@ -4041,11 +4123,11 @@
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="26"/>
+        <v>161</v>
+      </c>
+      <c r="C18" s="27"/>
       <c r="D18" s="15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G18" s="16" t="str">
         <f aca="false">IF(C18="","Skriv svaret i den gule cellen.",IF(ABS(C18-(ROUND((68000+3200)*0.2/(68000+3200)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C18-(ROUND((68000+3200)*0.2/((68000+3200)*1.2)*100,1)))&lt;=0.05,"Du har delt på prisen. Det er bruttofortjenesten (e). Avansen deles på inntakskosten.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
@@ -4054,11 +4136,11 @@
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="26"/>
+        <v>162</v>
+      </c>
+      <c r="C19" s="27"/>
       <c r="D19" s="15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G19" s="16" t="str">
         <f aca="false">IF(C19="","Skriv svaret i den gule cellen.",IF(ABS(C19-(ROUND((68000+3200)*0.2/((68000+3200)*1.2)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C19-(ROUND((68000+3200)*0.2/(68000+3200)*100,1)))&lt;=0.05,"Du har delt på inntakskosten. Det er avansen (d). Bruttofortjenesten deles på prisen, 85 440.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
@@ -4067,7 +4149,7 @@
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="15" t="s">
@@ -4080,7 +4162,7 @@
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="15" t="s">
@@ -4093,7 +4175,7 @@
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="15" t="s">
@@ -4106,7 +4188,7 @@
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="13" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C25" s="21"/>
       <c r="G25" s="16" t="str">
@@ -4116,7 +4198,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -4278,7 +4360,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Lager,svinn,bestilling,bundet kapital og en del av de indirekte kostnadene,Bare fortjeneste,Merverdiavgiften"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
@@ -4311,589 +4393,589 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>156</v>
+      <c r="B2" s="28" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>160</v>
+      <c r="B5" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>161</v>
+      <c r="B6" s="30" t="s">
+        <v>173</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>2671760</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>162</v>
+      <c r="D6" s="30" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="s">
-        <v>163</v>
+      <c r="B7" s="30" t="s">
+        <v>175</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>763</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>164</v>
+      <c r="D7" s="30" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
-        <v>165</v>
+      <c r="B8" s="30" t="s">
+        <v>177</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>299000</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>166</v>
+      <c r="D8" s="30" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>167</v>
+      <c r="B9" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>848.79</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>168</v>
+      <c r="D9" s="30" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>169</v>
+      <c r="B10" s="30" t="s">
+        <v>181</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>41.21</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>170</v>
+      <c r="D10" s="30" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="29" t="s">
-        <v>171</v>
+      <c r="B11" s="30" t="s">
+        <v>183</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>144240</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>172</v>
+      <c r="D11" s="30" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>173</v>
+      <c r="B12" s="30" t="s">
+        <v>185</v>
       </c>
       <c r="C12" s="12"/>
-      <c r="D12" s="29" t="s">
-        <v>174</v>
+      <c r="D12" s="30" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="29" t="s">
-        <v>175</v>
+      <c r="B13" s="30" t="s">
+        <v>187</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>586</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>176</v>
+      <c r="D13" s="30" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="29" t="s">
-        <v>177</v>
+      <c r="B14" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>4226000</v>
       </c>
-      <c r="D14" s="29" t="s">
-        <v>178</v>
+      <c r="D14" s="30" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="29" t="s">
-        <v>179</v>
+      <c r="B15" s="30" t="s">
+        <v>191</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>1194000</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>180</v>
+      <c r="D15" s="30" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="29" t="s">
-        <v>181</v>
+      <c r="B16" s="30" t="s">
+        <v>193</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>211</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>182</v>
+      <c r="D16" s="30" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="29" t="s">
-        <v>183</v>
+      <c r="B17" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>797</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>184</v>
+      <c r="D17" s="30" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="29" t="s">
-        <v>185</v>
+      <c r="B18" s="30" t="s">
+        <v>197</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="D18" s="29" t="s">
-        <v>186</v>
+      <c r="D18" s="30" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="29" t="s">
-        <v>187</v>
+      <c r="B19" s="30" t="s">
+        <v>199</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>890</v>
       </c>
-      <c r="D19" s="29" t="s">
-        <v>188</v>
+      <c r="D19" s="30" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="29" t="s">
-        <v>189</v>
+      <c r="B20" s="30" t="s">
+        <v>201</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>630</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>190</v>
+      <c r="D20" s="30" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="29" t="s">
-        <v>191</v>
+      <c r="B21" s="30" t="s">
+        <v>203</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>2400000</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>192</v>
+      <c r="D21" s="30" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="29" t="s">
-        <v>193</v>
+      <c r="B22" s="30" t="s">
+        <v>205</v>
       </c>
       <c r="C22" s="12"/>
-      <c r="D22" s="29" t="s">
-        <v>194</v>
+      <c r="D22" s="30" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="29" t="s">
-        <v>195</v>
+      <c r="B23" s="30" t="s">
+        <v>207</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>8960</v>
       </c>
-      <c r="D23" s="29" t="s">
-        <v>196</v>
+      <c r="D23" s="30" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="29" t="s">
-        <v>197</v>
+      <c r="B24" s="30" t="s">
+        <v>209</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>19560</v>
       </c>
-      <c r="D24" s="29" t="s">
-        <v>198</v>
+      <c r="D24" s="30" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="29" t="s">
-        <v>199</v>
+      <c r="B25" s="30" t="s">
+        <v>211</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>4200</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>200</v>
+      <c r="D25" s="30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="29" t="s">
-        <v>201</v>
+      <c r="B26" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>23760</v>
       </c>
-      <c r="D26" s="29" t="s">
-        <v>202</v>
+      <c r="D26" s="30" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="29" t="s">
-        <v>203</v>
+      <c r="B27" s="30" t="s">
+        <v>215</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>2851.2</v>
       </c>
-      <c r="D27" s="29" t="s">
-        <v>204</v>
+      <c r="D27" s="30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="29" t="s">
-        <v>205</v>
+      <c r="B28" s="30" t="s">
+        <v>217</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>26611.2</v>
       </c>
-      <c r="D28" s="29" t="s">
-        <v>206</v>
+      <c r="D28" s="30" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="29" t="s">
-        <v>207</v>
+      <c r="B29" s="30" t="s">
+        <v>219</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>6652.8</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>208</v>
+      <c r="D29" s="30" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="29" t="s">
-        <v>209</v>
+      <c r="B30" s="30" t="s">
+        <v>221</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>33264</v>
       </c>
-      <c r="D30" s="29" t="s">
-        <v>210</v>
+      <c r="D30" s="30" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="29" t="s">
-        <v>211</v>
+      <c r="B31" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="C31" s="12"/>
-      <c r="D31" s="29" t="s">
-        <v>212</v>
+      <c r="D31" s="30" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="29" t="s">
-        <v>213</v>
+      <c r="B32" s="30" t="s">
+        <v>225</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>4.5</v>
       </c>
-      <c r="D32" s="29" t="s">
-        <v>214</v>
+      <c r="D32" s="30" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="29" t="s">
-        <v>215</v>
+      <c r="B33" s="30" t="s">
+        <v>227</v>
       </c>
       <c r="C33" s="12"/>
-      <c r="D33" s="29" t="s">
-        <v>216</v>
+      <c r="D33" s="30" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="29" t="s">
-        <v>217</v>
+      <c r="B34" s="30" t="s">
+        <v>229</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>-1760</v>
       </c>
-      <c r="D34" s="29" t="s">
-        <v>218</v>
+      <c r="D34" s="30" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="29" t="s">
-        <v>219</v>
+      <c r="B35" s="30" t="s">
+        <v>231</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>2440</v>
       </c>
-      <c r="D35" s="29" t="s">
-        <v>220</v>
+      <c r="D35" s="30" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="29" t="s">
-        <v>221</v>
+      <c r="B36" s="30" t="s">
+        <v>233</v>
       </c>
       <c r="C36" s="12" t="n">
         <v>11.1</v>
       </c>
-      <c r="D36" s="29" t="s">
-        <v>222</v>
+      <c r="D36" s="30" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="29" t="s">
-        <v>223</v>
+      <c r="B37" s="30" t="s">
+        <v>235</v>
       </c>
       <c r="C37" s="12" t="n">
         <v>48800</v>
       </c>
-      <c r="D37" s="29" t="s">
-        <v>224</v>
+      <c r="D37" s="30" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="29" t="s">
-        <v>225</v>
+      <c r="B38" s="30" t="s">
+        <v>237</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>58.1</v>
       </c>
-      <c r="D38" s="29" t="s">
-        <v>226</v>
+      <c r="D38" s="30" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="29" t="s">
-        <v>227</v>
+      <c r="B39" s="30" t="s">
+        <v>239</v>
       </c>
       <c r="C39" s="12"/>
-      <c r="D39" s="29" t="s">
-        <v>228</v>
+      <c r="D39" s="30" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="29" t="s">
-        <v>229</v>
+      <c r="B40" s="30" t="s">
+        <v>241</v>
       </c>
       <c r="C40" s="12"/>
-      <c r="D40" s="29" t="s">
-        <v>230</v>
+      <c r="D40" s="30" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="29" t="s">
-        <v>231</v>
+      <c r="B41" s="30" t="s">
+        <v>243</v>
       </c>
       <c r="C41" s="12" t="n">
         <v>12160</v>
       </c>
-      <c r="D41" s="29" t="s">
-        <v>232</v>
+      <c r="D41" s="30" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="29" t="s">
-        <v>233</v>
+      <c r="B42" s="30" t="s">
+        <v>245</v>
       </c>
       <c r="C42" s="12" t="n">
         <v>-3200</v>
       </c>
-      <c r="D42" s="29" t="s">
-        <v>234</v>
+      <c r="D42" s="30" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="29" t="s">
-        <v>235</v>
+      <c r="B43" s="30" t="s">
+        <v>247</v>
       </c>
       <c r="C43" s="12" t="n">
         <v>22760</v>
       </c>
-      <c r="D43" s="29" t="s">
-        <v>236</v>
+      <c r="D43" s="30" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="29" t="s">
-        <v>237</v>
+      <c r="B44" s="30" t="s">
+        <v>249</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>26960</v>
       </c>
-      <c r="D44" s="29" t="s">
-        <v>238</v>
+      <c r="D44" s="30" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="29" t="s">
-        <v>239</v>
+      <c r="B45" s="30" t="s">
+        <v>251</v>
       </c>
       <c r="C45" s="12" t="n">
         <v>-348.8</v>
       </c>
-      <c r="D45" s="29" t="s">
-        <v>240</v>
+      <c r="D45" s="30" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="29" t="s">
-        <v>241</v>
+      <c r="B46" s="30" t="s">
+        <v>253</v>
       </c>
       <c r="C46" s="12"/>
-      <c r="D46" s="29" t="s">
-        <v>242</v>
+      <c r="D46" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="29" t="s">
-        <v>243</v>
+      <c r="B47" s="30" t="s">
+        <v>254</v>
       </c>
       <c r="C47" s="12" t="n">
         <v>37744</v>
       </c>
-      <c r="D47" s="29" t="s">
-        <v>244</v>
+      <c r="D47" s="30" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="29" t="s">
-        <v>245</v>
+      <c r="B48" s="30" t="s">
+        <v>256</v>
       </c>
       <c r="C48" s="12"/>
-      <c r="D48" s="29" t="s">
-        <v>246</v>
+      <c r="D48" s="30" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="29" t="s">
-        <v>247</v>
+      <c r="B49" s="30" t="s">
+        <v>258</v>
       </c>
       <c r="C49" s="12" t="n">
         <v>71200</v>
       </c>
-      <c r="D49" s="29" t="s">
-        <v>248</v>
+      <c r="D49" s="30" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="29" t="s">
-        <v>249</v>
+      <c r="B50" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>85440</v>
       </c>
-      <c r="D50" s="29" t="s">
-        <v>250</v>
+      <c r="D50" s="30" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="29" t="s">
-        <v>251</v>
+      <c r="B51" s="30" t="s">
+        <v>262</v>
       </c>
       <c r="C51" s="12" t="n">
         <v>14240</v>
       </c>
-      <c r="D51" s="29" t="s">
-        <v>252</v>
+      <c r="D51" s="30" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="29" t="s">
-        <v>253</v>
+      <c r="B52" s="30" t="s">
+        <v>264</v>
       </c>
       <c r="C52" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="D52" s="29" t="s">
-        <v>254</v>
+      <c r="D52" s="30" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="29" t="s">
-        <v>255</v>
+      <c r="B53" s="30" t="s">
+        <v>266</v>
       </c>
       <c r="C53" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="D53" s="29" t="s">
-        <v>256</v>
+      <c r="D53" s="30" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="29" t="s">
-        <v>257</v>
+      <c r="B54" s="30" t="s">
+        <v>268</v>
       </c>
       <c r="C54" s="12" t="n">
         <v>106800</v>
       </c>
-      <c r="D54" s="29" t="s">
-        <v>258</v>
+      <c r="D54" s="30" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="29" t="s">
-        <v>259</v>
+      <c r="B55" s="30" t="s">
+        <v>270</v>
       </c>
       <c r="C55" s="12" t="n">
         <v>97280</v>
       </c>
-      <c r="D55" s="29" t="s">
-        <v>260</v>
+      <c r="D55" s="30" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="29" t="s">
-        <v>261</v>
+      <c r="B56" s="30" t="s">
+        <v>272</v>
       </c>
       <c r="C56" s="12" t="n">
         <v>3072</v>
       </c>
-      <c r="D56" s="29" t="s">
-        <v>262</v>
+      <c r="D56" s="30" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="29" t="s">
-        <v>263</v>
+      <c r="B57" s="30" t="s">
+        <v>274</v>
       </c>
       <c r="C57" s="12"/>
-      <c r="D57" s="29" t="s">
-        <v>264</v>
+      <c r="D57" s="30" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="29" t="s">
-        <v>265</v>
+      <c r="B58" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="C58" s="12"/>
-      <c r="D58" s="29" t="s">
-        <v>266</v>
+      <c r="D58" s="30" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok05/OK05_Kalkulasjon_Oppgaver_v6.xlsx
+++ b/pensum/ok05/OK05_Kalkulasjon_Oppgaver_v6.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">1C  Fastpris til Hansen: hele selvkostkalkylen på jobb 2614</t>
   </si>
   <si>
-    <t xml:space="preserve">2A  20 skap til 22 000 kr i en stille januar: ta jobben?</t>
+    <t xml:space="preserve">2A  20 skap til 22 000 kr i en stille uke i august: ta jobben?</t>
   </si>
   <si>
     <t xml:space="preserve">2B  Etterkalkylen på jobb 2614: holdt forkalkylen?</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Tallene fra Nordlys' resultatregnskap 2026, i kroner</t>
   </si>
   <si>
-    <t xml:space="preserve">Lønn og sosiale kostnader: montører og lærlinger 8 440 000, administrasjon 2 220 000. Avskrivninger 620 000. Andre driftskostnader (husleie, biler, forsikring, IT) 1 386 000. Varekostnad (materiell og innleie) 8 390 000. Salgsinntekt 22 400 000, hvorav timer 14 400 × 890 = 12 816 000 og materiell 9 584 000. Driftsresultat 1 344 000. Montørene er på jobb 20 340 timer; 14 400 blir fakturert.</t>
+    <t xml:space="preserve">Lønn og sosiale kostnader: montører og lærlinger 8 440 000, administrasjon 2 220 000. Avskrivninger 620 000. Andre driftskostnader (husleie, biler, forsikring, IT) 1 386 000. Varekostnad 8 390 000: materiell 7 990 000 og innleide montører 400 000. Salgsinntekt 22 400 000, hvorav timer 14 400 × 890 = 12 816 000 og materiell 9 584 000. Driftsresultat 1 344 000. Montørene er på jobb 20 340 timer; 14 400 blir fakturert.</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys' timepris, per fakturert time</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">Direkte lønn per time (8 440 000 / 14 400)</t>
   </si>
   <si>
-    <t xml:space="preserve">Indirekte kostnader i året</t>
+    <t xml:space="preserve">Indirekte kostnader og innleie i året</t>
   </si>
   <si>
     <t xml:space="preserve">Dekket av påslaget på materiellet</t>
   </si>
   <si>
-    <t xml:space="preserve">Indirekte per time, etter påslaget</t>
+    <t xml:space="preserve">Indirekte og innleie per time, etter påslaget</t>
   </si>
   <si>
     <t xml:space="preserve">Selvkost per time</t>
@@ -194,8 +194,8 @@
     <t xml:space="preserve">Timepris uten merverdiavgift</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Fyll inn oppstillingen linje for linje. Direkte lønn er montører og lærlinger delt på de fakturerte timene. Det indirekte er administrasjon, avskrivninger og andre driftskostnader, men påslaget på materiellet dekker en del: materiellinntekten minus varekostnaden.
-2. Selvkost per time er direkte lønn pluss indirekte per time. Legg til fortjenesten, og du skal lande på 890.
+    <t xml:space="preserve">1. Fyll inn oppstillingen linje for linje. Direkte lønn er montører og lærlinger delt på de fakturerte timene. Det indirekte er administrasjon, avskrivninger og andre driftskostnader. De innleide montørene, 400 000, tas med her, fordi timene deres selges som timer og ikke ligger i materiellet. Påslaget på materiellet dekker en del: materiellinntekten minus materialkostnaden, 7 990 000 (uten innleie).
+2. Selvkost per time er direkte lønn pluss indirekte og innleie per time. Legg til fortjenesten, og du skal lande på 890.
 3. Regn fella i h og i, og skriv svaret til Tom og Ronny i j.</t>
   </si>
   <si>
@@ -205,16 +205,16 @@
     <t xml:space="preserve">Direkte lønnskostnad per time:</t>
   </si>
   <si>
-    <t xml:space="preserve">Indirekte i året:</t>
+    <t xml:space="preserve">Indirekte og innleie i året:</t>
   </si>
   <si>
     <t xml:space="preserve">Dekket av påslaget på materiellet:</t>
   </si>
   <si>
-    <t xml:space="preserve">Indirekte per fakturert time:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selvkost per fakturert time:</t>
+    <t xml:space="preserve">Indirekte og innleie per fakturert time:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bokas selvkost per time:</t>
   </si>
   <si>
     <t xml:space="preserve">Fortjeneste per time:</t>
@@ -339,7 +339,7 @@
     <t xml:space="preserve">Si nei til 22 000: jobben fortrenger jobber til normalpris</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppgave 2A: 20 skap til 22 000 kr i en stille januar: ta jobben?</t>
+    <t xml:space="preserve">Oppgave 2A: 20 skap til 22 000 kr i en stille uke i august: ta jobben?</t>
   </si>
   <si>
     <t xml:space="preserve">Si ja: dekningsbidraget er positivt</t>
@@ -348,13 +348,13 @@
     <t xml:space="preserve">Si ja, men bare for ti skap</t>
   </si>
   <si>
-    <t xml:space="preserve">Januar 2027. Ordreboka er tynn, og fire montører har lite å gjøre de neste tre ukene. Et boligbyggelag vil ha byttet 20 sikringsskap av samme type som hos Hansen, og tilbyr 22 000 kr per skap uten merverdiavgift. Tom sier nei: under selvkost. Kari sier ja: husleia, kontoret og bilene koster det samme uansett.</t>
+    <t xml:space="preserve">August 2027, rett etter fellesferien. Ordreboka er tynn, og fire montører har lite å gjøre de neste tre ukene. Styret i et borettslag, med boligbyggelaget som forretningsfører, ber om pris på å bytte 20 sikringsskap av samme type som hos Hansen. Prisen de har fått fra en konkurrent, er 22 000 kr per skap uten merverdiavgift. Tom sier nei: under selvkost. Kari sier ja: husleia, kontoret og bilene koster det samme uansett.</t>
   </si>
   <si>
     <t xml:space="preserve">Merkost (minimumskost) = direkte kostnader + indirekte variable kostnader; hos Nordlys er de indirekte faste, så merkost er de direkte kostnadene. Dekningsbidrag = pris − merkost. Dekningsgrad = dekningsbidrag / pris. Regel for pristilbud: bidragsmetoden ved ledig kapasitet, i lavsesong og i krisetid; ellers selvkost, fordi de faste kostnadene må dekkes av alt arbeidet i året.</t>
   </si>
   <si>
-    <t xml:space="preserve">Per skap gjelder kalkylen fra jobb 2614: direkte kostnader 19 560 kr (14 timer × 640, materiell 9 800, kjøring 800), indirekte 4 200 kr, selvkost 23 760 kr, normalpris 26 611,20 kr uten merverdiavgift. Boligbyggelaget tilbyr 22 000 kr per skap uten merverdiavgift for 20 skap. Nordlys regner de indirekte kostnadene som faste, så merkost er de direkte kostnadene.</t>
+    <t xml:space="preserve">Per skap gjelder kalkylen fra jobb 2614: direkte kostnader 19 560 kr (14 timer × 640, materiell 9 800, kjøring 800), indirekte 4 200 kr, selvkost 23 760 kr, normalpris 26 611,20 kr uten merverdiavgift. Styret i et borettslag ber om pris på 20 skap, og en konkurrent har gitt 22 000 kr per skap uten merverdiavgift. Spørsmålet er om Nordlys skal by 22 000 kr. Nordlys regner de indirekte kostnadene som faste, så merkost er de direkte kostnadene. a–e følger bokas bidragskalkyle, der montørlønna er en direkte kostnad. Men de fire montørene er fast ansatt og får lønn i august uansett. Med ledig kapasitet er den faktiske merkosten bare materiell og kjøring, 9 800 + 800 = 10 600 kr, og dekningsbidraget 22 000 − 10 600 = 11 400 kr per skap, 228 000 kr for 20 skap. Bruk begge tallene i g.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Regn resultatet per skap etter selvkostkalkylen: pris minus selvkost (a). Negativt tall betyr tap.
@@ -381,10 +381,10 @@
     <t xml:space="preserve">e) De 20 skapene skulle båret 20 × 4 200 = 84 000 kr i indirekte kostnader. Hvor stor del dekker dekningsbidraget? Prosent med én desimal</t>
   </si>
   <si>
-    <t xml:space="preserve">f) Samme forespørsel kommer i mai, når alle montørene er booket på jobber til normalpris i seks uker. Hva bør Nordlys gjøre?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g) Etter januar vil Tom bruke 22 000 kr som fast pris på alle skapbytter resten av året, siden «dekningsbidraget er positivt». Hva sier du til ham? To setninger med tall.</t>
+    <t xml:space="preserve">f) Samme forespørsel kommer i oktober, når alle montørene er booket på jobber til normalpris i seks uker. Hva bør Nordlys gjøre?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g) Etter august vil Tom bruke 22 000 kr som fast pris på alle skapbytter resten av året, siden «dekningsbidraget er positivt». Hva sier du til ham? To setninger med tall.</t>
   </si>
   <si>
     <t xml:space="preserve">Kostnaden ble høyere enn kalkulert</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">Merverdiavgiften</t>
   </si>
   <si>
-    <t xml:space="preserve">Ida har bestilt et parti downlights fra Polarlys til et borettslag. Nordlys fakturerer materiellet videre med 20 % påslag på inntakskosten. Kunden har sett prisen i en nettbutikk og spør hvorfor Nordlys tar mer. Og Tom lurer på hvorfor 40 % pluss 12 % i bokas eksempel ikke blir 52 %.</t>
+    <t xml:space="preserve">Ronny har bestilt et parti downlights fra Polarlys til et borettslag. Nordlys fakturerer materiellet videre med 20 % påslag på inntakskosten. Kunden har sett prisen i en nettbutikk og spør hvorfor Nordlys tar mer. Og Tom lurer på hvorfor 40 % pluss 12 % i bokas eksempel ikke blir 52 %.</t>
   </si>
   <si>
     <t xml:space="preserve">Inntakskost = innkjøpspris + innkjøpskostnader (frakt, forsikring, toll); det samme som varekostnaden. Avanse = pris uten merverdiavgift − inntakskost; i prosent av inntakskost. Bruttofortjeneste = de samme kronene i prosent av prisen uten merverdiavgift. Prosenter oppå prosenter ganges: 1,40 × 1,12 = 1,568, ikke 1,52.</t>
@@ -611,28 +611,28 @@
     <t xml:space="preserve">8 440 000 / 14 400 = 586 kr</t>
   </si>
   <si>
-    <t xml:space="preserve">1B Indirekte i året</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 220 000 + 620 000 + 1 386 000 = 4 226 000 kr</t>
+    <t xml:space="preserve">1B Indirekte og innleie i året</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 220 000 + 620 000 + 1 386 000 + 400 000 = 4 626 000 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1B Dekket av materiellpåslaget</t>
   </si>
   <si>
-    <t xml:space="preserve">9 584 000 − 8 390 000 = 1 194 000 kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1B Indirekte per time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4 226 000 − 1 194 000) / 14 400 = 211 kr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1B Selvkost per time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">586 + 211 = 797 kr</t>
+    <t xml:space="preserve">9 584 000 − 7 990 000 = 1 594 000 kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1B Indirekte og innleie per time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4 626 000 − 1 594 000) / 14 400 = 211 kr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1B Bokas selvkost per time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">586 + 211 = 797 kr, etter at materialpåslaget har betalt sin del. Selvkost per fakturert time, når timene alene skal bære de indirekte kostnadene, er 586 + 321 = 907 kr ((21 056 000 − 7 990 000) / 14 400), mer enn timeprisen 890: påslaget subsidierer timene</t>
   </si>
   <si>
     <t xml:space="preserve">1B Fortjeneste per time</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">48 800 / 84 000 = 58,1 %</t>
   </si>
   <si>
-    <t xml:space="preserve">2A f) I mai</t>
+    <t xml:space="preserve">2A f) I oktober</t>
   </si>
   <si>
     <t xml:space="preserve">Nei: uten ledig kapasitet fortrenger jobben jobber til normalpris. Selvkost gjelder</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">2A g) Til Tom</t>
   </si>
   <si>
-    <t xml:space="preserve">2 440 dekker 58 % av 4 200 og gir null i fortjeneste. De faste kostnadene må dekkes av hele året. Bidragspris bare ved ledig kapasitet</t>
+    <t xml:space="preserve">I august er lønna betalt uansett, så skapet gir 11 400 kr hver (228 000 for 20). Som fast pris dekker 2 440 bare 58 % av 4 200 og gir null i fortjeneste. Bidragspris bare ved ledig kapasitet</t>
   </si>
   <si>
     <t xml:space="preserve">2B Direkte lønn, etterkalkyle</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">2B e) Neste tilbud</t>
   </si>
   <si>
-    <t xml:space="preserve">Skriv om forkalkylen (19 timer, 37 744 kr) eller få timene ned (befaring, ferdig plukket materiell). Finn årsaken først</t>
+    <t xml:space="preserve">Skriv om forkalkylen (19 timer, 37 744 kr) eller få timene ned (befaring, ferdig plukket materiell). Finn årsaken først; i eldre boliger er det ofte jording som må utbedres og overspenningsvern som må monteres, og det tas forbehold om i fastprisen</t>
   </si>
   <si>
     <t xml:space="preserve">2C a) Inntakskost</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">2C j) Til kunden</t>
   </si>
   <si>
-    <t xml:space="preserve">Lager og bestilling, garanti på installasjonen, dokumentasjon til samsvarserklæringen. Nettbutikken monterer ikke</t>
+    <t xml:space="preserve">Lager og bestilling, montasje, reklamasjonsrett på arbeidet, dokumentasjon til samsvarserklæringen. Nettbutikken monterer ikke</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2079,7 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
     </row>
-    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="s">
         <v>54</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>57</v>
       </c>
       <c r="C25" s="24" t="str">
-        <f aca="false">IF(C13="","Skriv svaret i cellen C13.",IF(C13=(2220000+620000+1386000),"Riktig.",IF(ABS(C13-(2220000+1386000))&lt;=0,"Du har glemt avskrivningene, 620 000.",IF(ABS(C13-(620000+1386000))&lt;=0,"Du har glemt administrasjonslønna, 2 220 000. Den er indirekte: Kari og Ida jobber for alle jobbene.","Ikke riktig ennå. Administrasjon 2 220 000 + avskrivninger 620 000 + andre driftskostnader 1 386 000."))))</f>
+        <f aca="false">IF(C13="","Skriv svaret i cellen C13.",IF(C13=(2220000+620000+1386000+400000),"Riktig.",IF(ABS(C13-(2220000+1386000+400000))&lt;=0,"Du har glemt avskrivningene, 620 000.",IF(ABS(C13-(620000+1386000+400000))&lt;=0,"Du har glemt administrasjonslønna, 2 220 000. Den er indirekte: Kari og Ida jobber for alle jobbene.",IF(ABS(C13-(2220000+620000+1386000))&lt;=0,"Du har glemt de innleide montørene, 400 000. Timene deres selges som timer, så timeprisen må bære dem.","Ikke riktig ennå. Administrasjon 2 220 000 + avskrivninger 620 000 + andre driftskostnader 1 386 000 + innleide montører 400 000.")))))</f>
         <v>Skriv svaret i cellen C13.</v>
       </c>
       <c r="D25" s="24"/>
@@ -2125,7 +2125,7 @@
         <v>58</v>
       </c>
       <c r="C26" s="24" t="str">
-        <f aca="false">IF(C14="","Skriv svaret i cellen C14.",IF(C14=(9584000-8390000),"Riktig.",IF(ABS(C14-(9584000))&lt;=0,"Det er hele materiellinntekten. Trekk fra varekostnaden, 8 390 000; det er bare påslaget som dekker indirekte.",IF(ABS(C14-(8390000))&lt;=0,"Det er varekostnaden. Påslaget er materiellinntekt minus varekostnad.","Ikke riktig ennå. Materiellinntekt 9 584 000 minus varekostnad 8 390 000."))))</f>
+        <f aca="false">IF(C14="","Skriv svaret i cellen C14.",IF(C14=(9584000-7990000),"Riktig.",IF(ABS(C14-(9584000))&lt;=0,"Det er hele materiellinntekten. Trekk fra materialkostnaden, 7 990 000; det er bare påslaget som dekker indirekte.",IF(ABS(C14-(9584000-8390000))&lt;=0,"Du har trukket fra hele varekostnaden. 400 000 av den er innleide montører, som aldri ligger i materiellet. Trekk fra materialkostnaden, 7 990 000.",IF(ABS(C14-(7990000))&lt;=0,"Det er materialkostnaden. Påslaget er materiellinntekt minus materialkostnad.","Ikke riktig ennå. Materiellinntekt 9 584 000 minus materialkostnad 7 990 000.")))))</f>
         <v>Skriv svaret i cellen C14.</v>
       </c>
       <c r="D26" s="24"/>
@@ -2138,7 +2138,7 @@
         <v>59</v>
       </c>
       <c r="C27" s="24" t="str">
-        <f aca="false">IF(C15="","Skriv svaret i cellen C15.",IF(C15=(ROUND((2220000+620000+1386000-(9584000-8390000))/14400,0)),"Riktig.",IF(ABS(C15-(ROUND((2220000+620000+1386000)/14400,0)))&lt;=0,"Du har ikke trukket fra det påslaget på materiellet dekker. Da betaler kunden for det samme to ganger.",IF(ABS(C15-(ROUND((2220000+620000+1386000-(9584000-8390000))/20340,0)))&lt;=0,"Du har delt på 20 340 timer. Del på de 14 400 som faktureres.","Ikke riktig ennå. Indirekte i året minus det påslaget dekker, delt på 14 400."))))</f>
+        <f aca="false">IF(C15="","Skriv svaret i cellen C15.",IF(C15=(ROUND((2220000+620000+1386000+400000-(9584000-7990000))/14400,0)),"Riktig.",IF(ABS(C15-(ROUND((2220000+620000+1386000+400000)/14400,0)))&lt;=0,"Du har ikke trukket fra det påslaget på materiellet dekker. Da betaler kunden for det samme to ganger.",IF(ABS(C15-(ROUND((2220000+620000+1386000+400000-(9584000-7990000))/20340,0)))&lt;=0,"Du har delt på 20 340 timer. Del på de 14 400 som faktureres.","Ikke riktig ennå. Indirekte og innleie i året minus det påslaget dekker, delt på 14 400."))))</f>
         <v>Skriv svaret i cellen C15.</v>
       </c>
       <c r="D27" s="24"/>
@@ -2151,7 +2151,7 @@
         <v>60</v>
       </c>
       <c r="C28" s="24" t="str">
-        <f aca="false">IF(C16="","Skriv svaret i cellen C16.",IF(C16=(ROUND(8440000/14400,0)+ROUND((2220000+620000+1386000-(9584000-8390000))/14400,0)),"Riktig.",IF(ABS(C16-(ROUND(8440000/14400,0)))&lt;=0,"Det er bare den direkte lønna. Legg til det indirekte per time.","Ikke riktig ennå. Direkte lønn per time pluss indirekte per time.")))</f>
+        <f aca="false">IF(C16="","Skriv svaret i cellen C16.",IF(C16=(ROUND(8440000/14400,0)+ROUND((2220000+620000+1386000+400000-(9584000-7990000))/14400,0)),"Riktig.",IF(ABS(C16-(ROUND(8440000/14400,0)))&lt;=0,"Det er bare den direkte lønna. Legg til det indirekte og innleien per time.","Ikke riktig ennå. Direkte lønn per time pluss indirekte og innleie per time. Merk: 797 er bokas selvkost per time etter at materialpåslaget har betalt sin del. Selvkost per fakturert time, når timene alene skal bære de indirekte kostnadene, er 907 kr, mer enn 890.")))</f>
         <v>Skriv svaret i cellen C16.</v>
       </c>
       <c r="D28" s="24"/>
@@ -2177,7 +2177,7 @@
         <v>62</v>
       </c>
       <c r="C30" s="24" t="str">
-        <f aca="false">IF(C18="","Skriv svaret i cellen C18.",IF(C18=(ROUND(8440000/14400,0)+ROUND((2220000+620000+1386000-(9584000-8390000))/14400,0)+ROUND(1344000/14400,0)),"Riktig.","Ikke riktig ennå. Selvkost per time pluss fortjeneste per time. Skal bli 890."))</f>
+        <f aca="false">IF(C18="","Skriv svaret i cellen C18.",IF(C18=(ROUND(8440000/14400,0)+ROUND((2220000+620000+1386000+400000-(9584000-7990000))/14400,0)+ROUND(1344000/14400,0)),"Riktig.","Ikke riktig ennå. Selvkost per time pluss fortjeneste per time. Skal bli 890."))</f>
         <v>Skriv svaret i cellen C18.</v>
       </c>
       <c r="D30" s="24"/>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="19" t="str">
-        <f aca="false">IF(LEN(B38)&lt;40,"",IF(AND(ISNUMBER(SEARCH("586",B38)),ISNUMBER(SEARCH("timer",B38))),"Bra: du bruker både 586 kr i lønn og timene. Lønna kan ikke flyttes mye; det er timene som flytter prisen, og bransjen fakturerer 87 % mot Nordlys' 70,8 %.",IF(OR(ISNUMBER(SEARCH("586",B38)),ISNUMBER(SEARCH("timer",B38))),"Du er på sporet. Ta med at lønna er 586 av 890 og styres av tariffen, og at det er antall fakturerte timer som flytter prisen mest.","Tips: 586 av 890 går til lønn, 211 til det indirekte og 93 er fortjeneste. Lønna følger tariffen. Det som flytter prisen, er timene: flere fakturerte timer gjør hver time billigere å bære.")))</f>
+        <f aca="false">IF(LEN(B38)&lt;40,"",IF(AND(ISNUMBER(SEARCH("586",B38)),ISNUMBER(SEARCH("timer",B38))),"Bra: du bruker både 586 kr i lønn og timene. Lønna kan ikke flyttes mye; det er timene som flytter prisen, og bransjen fakturerer 87 % mot Nordlys' 70,8 %.",IF(OR(ISNUMBER(SEARCH("586",B38)),ISNUMBER(SEARCH("timer",B38))),"Du er på sporet. Ta med at lønna er 586 av 890 og styres av tariffen, og at det er antall fakturerte timer som flytter prisen mest.","Tips: 586 av 890 går til egen montørlønn, 211 til det indirekte og innleien, og 93 er fortjeneste. Lønna følger tariffen. Det som flytter prisen, er timene: flere fakturerte timer gjør hver time billigere å bære.")))</f>
         <v/>
       </c>
       <c r="C41" s="19"/>
@@ -2282,9 +2282,9 @@
       </c>
       <c r="C42" s="21"/>
     </row>
-    <row r="43" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="22" t="str">
-        <f aca="false">IF(C42="JA","Hint: Direkte lønn 8 440 000 / 14 400 = 586. Indirekte 2 220 000 + 620 000 + 1 386 000 = 4 226 000; påslaget dekker 9 584 000 − 8 390 000 = 1 194 000; (4 226 000 − 1 194 000) / 14 400 = 211. Selvkost 797. Fortjeneste 1 344 000 / 14 400 = 93. Timepris 890. Fella: 12 816 000 / 20 340 = 630; 11 472 000 − 630 × 14 400 = 2 400 000.","")</f>
+        <f aca="false">IF(C42="JA","Hint: Direkte lønn 8 440 000 / 14 400 = 586. Indirekte og innleie 2 220 000 + 620 000 + 1 386 000 + 400 000 = 4 626 000; påslaget dekker 9 584 000 − 7 990 000 = 1 594 000; (4 626 000 − 1 594 000) / 14 400 = 211. Bokas selvkost 797 (selvkost per fakturert time, når timene alene bærer de indirekte kostnadene: 907, mer enn timeprisen). Fortjeneste 1 344 000 / 14 400 = 93. Timepris 890. Fella: 12 816 000 / 20 340 = 630; 11 472 000 − 630 × 14 400 = 2 400 000.","")</f>
         <v/>
       </c>
       <c r="C43" s="22"/>
@@ -3004,7 +3004,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>104</v>
       </c>
@@ -3044,7 +3044,7 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
         <v>106</v>
       </c>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C21" s="21"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Si nei til 22 000: jobben fortrenger jobber til normalpris","Riktig. Uten ledig kapasitet tar den billige jobben plassen til en jobb til 26 611. Da er alternativet for timene ikke null, og selvkostkalkylen gjelder.","Ikke riktig. Uten ledig kapasitet tar den billige jobben plassen til en jobb til 26 611. Da er alternativet for timene ikke null, og selvkostkalkylen gjelder."))</f>
+        <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Si nei til 22 000: jobben fortrenger jobber til normalpris","Riktig. Uten ledig kapasitet tar den billige jobben plassen til en jobb til 26 611. Da er alternativet for timene ikke null: hver time som brukes på skapet, koster 890 kr i tapt fakturering (lønna betales uansett). Merkosten blir da 10 600 + 14 × 890 = 23 060 kr, over 22 000, og selvkostkalkylen gjelder.","Ikke riktig. Uten ledig kapasitet tar den billige jobben plassen til en jobb til 26 611. Da er alternativet for timene ikke null: hver time som brukes på skapet, koster 890 kr i tapt fakturering (lønna betales uansett). Merkosten blir da 10 600 + 14 × 890 = 23 060 kr, over 22 000, og selvkostkalkylen gjelder."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -3185,7 +3185,7 @@
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="19" t="str">
-        <f aca="false">IF(LEN(B24)&lt;40,"",IF(AND(ISNUMBER(SEARCH("faste",B24)),ISNUMBER(SEARCH("ledig",B24))),"Bra: du har med både de faste kostnadene og ledig kapasitet. 2 440 dekker bare 58 % av de 4 200 hvert skap skal bære, og gir null i fortjeneste; de faste kostnadene må dekkes av alt arbeidet i løpet av året.",IF(OR(ISNUMBER(SEARCH("faste",B24)),ISNUMBER(SEARCH("ledig",B24))),"Du er på sporet. Si både at de faste kostnadene må dekkes av hele året (2 440 dekker bare 58 % av 4 200), og at bidragsprisen bare gjelder ved ledig kapasitet.","Tips: 2 440 kr dekker 58 % av de 4 200 kr hvert skap skal bære av de faste, og gir null i fortjeneste. Januarprisen er et tilbud ved ledig kapasitet. Normalprisen er 26 611.")))</f>
+        <f aca="false">IF(LEN(B24)&lt;40,"",IF(AND(ISNUMBER(SEARCH("faste",B24)),ISNUMBER(SEARCH("ledig",B24))),"Bra: du har med både de faste kostnadene og ledig kapasitet. I august, med montører som ellers står ledige, gir hvert skap 11 400 kr mer enn det koster, fordi lønna betales uansett. Men som fast pris er 22 000 for lite: etter bokas kalkyle dekker 2 440 bare 58 % av de 4 200 hvert skap skal bære, og når kalenderen er full, fortrenger skapet jobber til normalpris.",IF(OR(ISNUMBER(SEARCH("faste",B24)),ISNUMBER(SEARCH("ledig",B24))),"Du er på sporet. Si både at de faste kostnadene må dekkes av hele året (2 440 dekker bare 58 % av 4 200), og at bidragsprisen bare gjelder ved ledig kapasitet.","Tips: i august er lønna betalt uansett, så skapet gir 22 000 − 10 600 = 11 400 kr. Som fast pris hele året dekker 2 440 kr bare 58 % av de 4 200 kr hvert skap skal bære av de faste, og gir null i fortjeneste. Augustprisen er et tilbud ved ledig kapasitet. Normalprisen er 26 611.")))</f>
         <v/>
       </c>
       <c r="C27" s="19"/>
@@ -3200,9 +3200,9 @@
       </c>
       <c r="C28" s="21"/>
     </row>
-    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="22" t="str">
-        <f aca="false">IF(C28="JA","Hint: a: 22 000 − 23 760 = −1 760. b: 22 000 − 19 560 = 2 440. c: 2 440 / 22 000 = 11,1 %. d: 20 × 2 440 = 48 800. e: 48 800 / 84 000 = 58,1 %.","")</f>
+        <f aca="false">IF(C28="JA","Hint: a: 22 000 − 23 760 = −1 760. b: 22 000 − 19 560 = 2 440. c: 2 440 / 22 000 = 11,1 %. d: 20 × 2 440 = 48 800. e: 48 800 / 84 000 = 58,1 %. Med fast lønn og ledige montører: 22 000 − 10 600 = 11 400 per skap, 228 000 for 20 skap.","")</f>
         <v/>
       </c>
       <c r="C29" s="22"/>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="19" t="str">
-        <f aca="false">IF(LEN(B41)&lt;40,"",IF(AND(ISNUMBER(SEARCH("timer",B41)),ISNUMBER(SEARCH("pris",B41))),"Bra: du har med både timene og prisen. Enten skrives forkalkylen om med 19 timer (37 744 kr med merverdiavgift, 13,5 % høyere), eller timene må ned med befaring og ferdig plukket materiell. Finn årsaken først.",IF(OR(ISNUMBER(SEARCH("timer",B41)),ISNUMBER(SEARCH("pris",B41))),"Du er på sporet. Ta med både forkalkylen (19 timer gir 37 744 kr) og gjennomføringen (befaring, ferdig plukket materiell), og si hvilken som gjelder.","Tips: 19 timer i forkalkylen gir 37 744 kr med merverdiavgift, 13,5 % høyere. Eller få timene ned: befaring, ferdig plukket materiell, én tur til grossisten. Var det gammelt anlegg eller dårlig planlegging? Svaret avgjør.")))</f>
+        <f aca="false">IF(LEN(B41)&lt;40,"",IF(AND(ISNUMBER(SEARCH("timer",B41)),ISNUMBER(SEARCH("pris",B41))),"Bra: du har med både timene og prisen. Enten skrives forkalkylen om med 19 timer (37 744 kr med merverdiavgift, 13,5 % høyere), eller timene må ned med befaring og ferdig plukket materiell. Finn årsaken først: i eldre boliger er det ofte jording som må utbedres og overspenningsvern som må monteres, og det tas forbehold om i fastprisen.",IF(OR(ISNUMBER(SEARCH("timer",B41)),ISNUMBER(SEARCH("pris",B41))),"Du er på sporet. Ta med både forkalkylen (19 timer gir 37 744 kr) og gjennomføringen (befaring, ferdig plukket materiell), og si hvilken som gjelder.","Tips: 19 timer i forkalkylen gir 37 744 kr med merverdiavgift, 13,5 % høyere. Eller få timene ned: befaring, ferdig plukket materiell, én tur til grossisten. Var det gammelt anlegg eller dårlig planlegging? Svaret avgjør. I eldre boliger er det ofte jording som må utbedres og overspenningsvern som må monteres; ta forbehold om det i fastprisen.")))</f>
         <v/>
       </c>
       <c r="C44" s="19"/>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="C25" s="21"/>
       <c r="G25" s="16" t="str">
-        <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Lager, svinn, bestilling, bundet kapital og en del av de indirekte kostnadene","Riktig. Påslaget regnes av inntakskosten og skal dekke kostnadene ved å ha materiellet: lager, svinn, bestilling og pengene som er bundet. Hos Nordlys dekker det også 1 194 000 kr av de indirekte kostnadene. Fortjenesten er bare en del av det.","Ikke riktig. Påslaget regnes av inntakskosten og skal dekke kostnadene ved å ha materiellet: lager, svinn, bestilling og pengene som er bundet. Hos Nordlys dekker det også 1 194 000 kr av de indirekte kostnadene. Fortjenesten er bare en del av det."))</f>
+        <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Lager, svinn, bestilling, bundet kapital og en del av de indirekte kostnadene","Riktig. Påslaget regnes av inntakskosten og skal dekke kostnadene ved å ha materiellet: lager, svinn, bestilling og pengene som er bundet. Hos Nordlys dekker det også 1 594 000 kr av de indirekte kostnadene. Fortjenesten er bare en del av det.","Ikke riktig. Påslaget regnes av inntakskosten og skal dekke kostnadene ved å ha materiellet: lager, svinn, bestilling og pengene som er bundet. Hos Nordlys dekker det også 1 594 000 kr av de indirekte kostnadene. Fortjenesten er bare en del av det."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="19" t="str">
-        <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("lager",B28)),ISNUMBER(SEARCH("garanti",B28))),"Bra: du har med både lageret og garantien. Prisen dekker lager og bestilling, garanti på installasjonen og dokumentasjonen til samsvarserklæringen; nettbutikken monterer ikke.",IF(OR(ISNUMBER(SEARCH("lager",B28)),ISNUMBER(SEARCH("garanti",B28))),"Du er på sporet. Ta med hva som ligger i prisen: lager og bestilling, garanti på installasjonen, og dokumentasjonen som følger anlegget.","Tips: prisen dekker lager, bestilling og svinn, garanti på installasjonen og dokumentasjonen til samsvarserklæringen. Nettbutikken monterer ikke og står ikke ansvarlig for anlegget.")))</f>
+        <f aca="false">IF(LEN(B28)&lt;40,"",IF(AND(ISNUMBER(SEARCH("lager",B28)),ISNUMBER(SEARCH("reklamasjon",B28))),"Bra: du har med både lageret og reklamasjonsretten. Prisen dekker lager og bestilling, montasje, reklamasjonsrett på arbeidet og dokumentasjonen til samsvarserklæringen; nettbutikken monterer ikke.",IF(OR(ISNUMBER(SEARCH("lager",B28)),ISNUMBER(SEARCH("reklamasjon",B28))),"Du er på sporet. Ta med hva som ligger i prisen: lager og bestilling, reklamasjonsrett på arbeidet, og dokumentasjonen som følger anlegget.","Tips: prisen dekker lager, bestilling og svinn, reklamasjonsrett på arbeidet og dokumentasjonen til samsvarserklæringen. Nettbutikken monterer ikke og står ikke ansvarlig for anlegget.")))</f>
         <v/>
       </c>
       <c r="C31" s="19"/>
@@ -4506,7 +4506,7 @@
         <v>189</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>4226000</v>
+        <v>4626000</v>
       </c>
       <c r="D14" s="30" t="s">
         <v>190</v>
@@ -4517,7 +4517,7 @@
         <v>191</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>1194000</v>
+        <v>1594000</v>
       </c>
       <c r="D15" s="30" t="s">
         <v>192</v>
@@ -4534,7 +4534,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="30" t="s">
         <v>195</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="30" t="s">
         <v>241</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="30" t="s">
         <v>256</v>
       </c>

--- a/pensum/ok05/OK05_Kalkulasjon_Oppgaver_v6.xlsx
+++ b/pensum/ok05/OK05_Kalkulasjon_Oppgaver_v6.xlsx
@@ -1470,7 +1470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1495,42 +1495,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1682,7 +1682,7 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="75.75" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
         <v>29</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
         <v>97</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
         <v>107</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
         <v>113</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
         <v>114</v>
       </c>
@@ -3549,7 +3549,7 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
     </row>
-    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="8" t="s">
         <v>134</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
         <v>148</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
         <v>164</v>
       </c>
